--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260729.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.33%</t>
+          <t>9.30%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.80%</t>
+          <t>8.91%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.11%</t>
+          <t>7.22%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.20%</t>
+          <t>6.21%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>5.74%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.41%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
@@ -792,73 +792,73 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>7,321,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台灣高鐵</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>7,259,000</t>
+          <t>86,095,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.15%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>台灣高鐵</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>85,748,000</t>
+          <t>264</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>13,731,000</t>
+          <t>39,763,500</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>39,763,500</t>
+          <t>13,731,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>98,618,000</t>
+          <t>99,084,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,29 +1007,29 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>17,879,000</t>
+          <t>17,973,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>3,423,000</t>
+          <t>1,705,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,127 +1041,127 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,705,000</t>
+          <t>3,423,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>36,919,540</t>
+          <t>21,432,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>8,032,000</t>
+          <t>56,078,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>21,373,000</t>
+          <t>8,032,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>55,601,000</t>
+          <t>36,919,540</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>27,877,000</t>
+          <t>10,742,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>10,742,000</t>
+          <t>2,276,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>8,334,000</t>
+          <t>8,422,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,39 +1217,39 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,220,678</t>
+          <t>28,042,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>3,577,000</t>
+          <t>17,902,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,22 +1261,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,276,000</t>
+          <t>3,577,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1298,90 +1298,90 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>17,902,000</t>
+          <t>2,220,678</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>16,825,000</t>
+          <t>17,258,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>17,258,000</t>
+          <t>16,825,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>16,986,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,39 +1393,39 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>3,863,000</t>
+          <t>16,986,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>3,863,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>4,749,000</t>
+          <t>4,769,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2,939,000</t>
+          <t>2,960,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1584,68 +1584,68 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>12,487,000</t>
+          <t>24,799,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24,248,000</t>
+          <t>12,487,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>32,953,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,22 +1657,22 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>32,953,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
